--- a/Rapid Cortex Internal Docs/Rapid_Cortex_SEO_Blog_Release_Calendar_v2_Distinct_Titles.xlsx
+++ b/Rapid Cortex Internal Docs/Rapid_Cortex_SEO_Blog_Release_Calendar_v2_Distinct_Titles.xlsx
@@ -411,13 +411,13 @@
     <t xml:space="preserve">Sep 15, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Rapid Cortex vs. Traditional CAD: What Is the Difference?</t>
+    <t xml:space="preserve">NexCort iQ vs. Traditional CAD: What Is the Difference?</t>
   </si>
   <si>
     <t xml:space="preserve">rapid-cortex-vs-traditional-cad</t>
   </si>
   <si>
-    <t xml:space="preserve">Rapid Cortex vs CAD</t>
+    <t xml:space="preserve">NexCort iQ vs CAD</t>
   </si>
   <si>
     <t xml:space="preserve">Sep 19, 2026</t>
@@ -993,7 +993,7 @@
     <t xml:space="preserve">multi-venue safety standard</t>
   </si>
   <si>
-    <t xml:space="preserve">Was a cross-vertical synthesis ('airports, arenas, and stadiums need...') that restated ground already covered by 'Why Rapid Cortex Is Needed,' 'Building a Safer Community,' and the airport post combined. Re-angled around a real, narrower audience: companies and authorities that operate more than one venue type and need one standard across them.</t>
+    <t xml:space="preserve">Was a cross-vertical synthesis ('airports, arenas, and stadiums need...') that restated ground already covered by 'Why NexCort iQ Is Needed,' 'Building a Safer Community,' and the airport post combined. Re-angled around a real, narrower audience: companies and authorities that operate more than one venue type and need one standard across them.</t>
   </si>
   <si>
     <t xml:space="preserve">Jan 26, 2027</t>
@@ -1104,31 +1104,31 @@
     <t xml:space="preserve">Slug</t>
   </si>
   <si>
-    <t xml:space="preserve">Why Rapid Cortex Is Needed: The Future of Real-Time Incident Intelligence</t>
+    <t xml:space="preserve">Why NexCort iQ Is Needed: The Future of Real-Time Incident Intelligence</t>
   </si>
   <si>
     <t xml:space="preserve">why-rapid-cortex-is-needed</t>
   </si>
   <si>
-    <t xml:space="preserve">Rapid Cortex Offerings: One Platform, Three Powerful Solutions</t>
+    <t xml:space="preserve">NexCort iQ Offerings: One Platform, Three Powerful Solutions</t>
   </si>
   <si>
     <t xml:space="preserve">rapid-cortex-offerings</t>
   </si>
   <si>
-    <t xml:space="preserve">Rapid Cortex Core: Modernizing Emergency Communications Without Replacing Existing Systems</t>
+    <t xml:space="preserve">NexCort iQ Core: Modernizing Emergency Communications Without Replacing Existing Systems</t>
   </si>
   <si>
     <t xml:space="preserve">rapid-cortex-core</t>
   </si>
   <si>
-    <t xml:space="preserve">Rapid Cortex Venue: Enhancing Safety Inside Stadiums, Arenas, Airports, and Large Gatherings</t>
+    <t xml:space="preserve">NexCort iQ Venue: Enhancing Safety Inside Stadiums, Arenas, Airports, and Large Gatherings</t>
   </si>
   <si>
     <t xml:space="preserve">rapid-cortex-venue</t>
   </si>
   <si>
-    <t xml:space="preserve">Rapid Cortex Campus: Empowering Students to Report Safety Concerns Instantly</t>
+    <t xml:space="preserve">NexCort iQ Campus: Empowering Students to Report Safety Concerns Instantly</t>
   </si>
   <si>
     <t xml:space="preserve">rapid-cortex-campus</t>
